--- a/MATERIALES.xlsx
+++ b/MATERIALES.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,25 +463,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 TINTA ROB</t>
+          <t>TINTAS NUTEC 6U - VIN.100CM GRIS Y BLANCO 4U</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55095.99</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>735165</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CH $265000 X3</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DIGITAL</t>
+          <t>IGENAR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>PAGADO</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>55095.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -490,25 +494,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 TINTAS ROB</t>
+          <t>LONA FRONT 110</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>220383.98</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>140200</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EFECTIVO</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIGITAL</t>
+          <t>NEA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>PAGADO</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>220383.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -517,20 +525,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARREGLO IMP210</t>
+          <t>BACK 137</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>771774.09</v>
+        <v>185000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CH $750000 TEJEDA 30 DIAS</t>
+          <t>EFECTIVO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIGITAL</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -548,20 +556,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3 TINTAS ROB</t>
+          <t>3 VINILOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>170526</v>
+        <v>341658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CH $176000 TACURU</t>
+          <t>CH $320552 25/08/26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIGITAL</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -579,20 +587,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRONT 120</t>
+          <t>3 LONAS FRONT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>157500</v>
+        <v>460297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EFECTIVO</t>
+          <t>CH $481403 11/08/26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEA </t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -610,11 +618,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PAPEL BLUEBACK</t>
+          <t>1 TINTA ROB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>209143.41</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -628,7 +636,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>209143.41</v>
+        <v>57812</v>
       </c>
     </row>
     <row r="8">
@@ -668,13 +676,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 TINTA ROB</t>
+          <t>PAPEL BLUEBACK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>209143.41</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EFECTIVO</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>DIGITAL</t>
@@ -682,7 +694,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>PAGADO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -695,20 +707,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3 LONAS FRONT</t>
+          <t>FRONT 120</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>460297</v>
+        <v>157500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CH $481403 11/08/26</t>
+          <t>EFECTIVO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t xml:space="preserve">NEA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -726,20 +738,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3 VINILOS</t>
+          <t>ARREGLO IMP210</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>341658</v>
+        <v>771774.09</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CH $320552 25/08/26</t>
+          <t>CH $750000 TEJEDA 30 DIAS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>DIGITAL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -757,20 +769,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BACK 137</t>
+          <t>3 TINTAS ROB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>185000</v>
+        <v>170526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EFECTIVO</t>
+          <t>CH $176000 TACURU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>DIGITAL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -790,11 +802,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LONA FRONT 110</t>
+          <t>4 TINTAS ROB</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>140200</v>
+        <v>220383.98</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -803,7 +815,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NEA</t>
+          <t>DIGITAL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -813,6 +825,126 @@
       </c>
       <c r="G13" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4 TINTAS ROB</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>234352</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>234352</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1 TINTA ROB</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>55095.99</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>55095.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6 LONAS FRONT 100/110/140/160</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>748186.5600000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CH $350000 10/10/26 - CH $398200 10/11/26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IGENAR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PAGADO</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2 VINILOS 100/127 - 1 MICRO 100</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>366116</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IGENAR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>366116</v>
       </c>
     </row>
   </sheetData>
